--- a/artfynd/A 9040-2023 artfynd.xlsx
+++ b/artfynd/A 9040-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9040-2023 artfynd.xlsx
+++ b/artfynd/A 9040-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>107098126</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589948.0340489069</v>
+        <v>589949</v>
       </c>
       <c r="R2" t="n">
-        <v>6392223.979188048</v>
+        <v>6392224</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -760,19 +755,9 @@
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -808,12 +793,7 @@
         <v>107098077</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589948.0340489069</v>
+        <v>589949</v>
       </c>
       <c r="R3" t="n">
-        <v>6392223.979188048</v>
+        <v>6392224</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -890,19 +870,9 @@
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-03-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
